--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-result.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-result.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="200">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Observation Result</t>
+    <t>Logical model - FR LM Observation Result</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:27:00+00:00</t>
+    <t>2026-04-24T08:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-entry</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -250,119 +250,391 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-observation-result.identifiant</t>
+    <t>fr-lm-observation-result.header</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>Métadonnées de base</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+</t>
+  </si>
+  <si>
+    <t>Patient/subject information</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.subject</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Identifiant de l'observation</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-result.code</t>
+    <t>Identifiant de l’entrée</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.identifier</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.author[x]</t>
+  </si>
+  <si>
+    <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
+  </si>
+  <si>
+    <t>Exécutant (performer)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.participant[x]</t>
+  </si>
+  <si>
+    <t>Participant</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.informant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
+</t>
+  </si>
+  <si>
+    <t>Informateur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.informant</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date/Heure de création par l'auteur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.date</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Code de l'observation</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-result.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.source</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.source</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.header.langue</t>
+  </si>
+  <si>
+    <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
+La partie en minuscules indique le code de la langue utilisée (ISO-639-1)
+La partie en majuscules indique le code pays (ISO-3166)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.langue</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.directSubject[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-devicehttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professionalhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedure</t>
+  </si>
+  <si>
+    <t>Sujet direct de l'observation si différent du patient, par exemple dans le cas d’une observation portant sur un dispositif implanté. D’autres types de sujets peuvent être autorisés selon les implémentations.</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.observationDate[x]</t>
+  </si>
+  <si>
+    <t>dateTime
+Period</t>
+  </si>
+  <si>
+    <t>Date de l'observation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.type</t>
+  </si>
+  <si>
+    <t>Type d'observation</t>
+  </si>
+  <si>
+    <t>LOINC (2.16.840.1.113883.6.1) ou autre</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.originalName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Description narrative de l'observation</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-result.statut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
+    <t>Nom de l'observation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.method</t>
+  </si>
+  <si>
+    <t>Méthode utilisée pour l'observation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.specimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-specimen
 </t>
   </si>
   <si>
-    <t>Statut de l'observation : completed</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-result.date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
+    <t>Prélèvement</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-service-request
 </t>
   </si>
   <si>
-    <t>Date/heure de l'observation</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-result.valeur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base
+    <t>Demande d'examen correspondante</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.bodySite</t>
+  </si>
+  <si>
+    <t>Localisation anatomique</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.result</t>
+  </si>
+  <si>
+    <t>Valeur de l'observation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.referenceRange</t>
+  </si>
+  <si>
+    <t>Intervalle de référence. Plusieurs intervalles de référence, de types différents, peuvent être fournis.</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.referenceRange.low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
 </t>
   </si>
   <si>
-    <t>Valeur observée</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-result.interpretation</t>
-  </si>
-  <si>
-    <t>Interprétation de la valeur (normal, anormal, etc.)</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-result.site</t>
-  </si>
-  <si>
-    <t>Site de l'observation</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-result.auteur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-auteur
-</t>
-  </si>
-  <si>
-    <t>Auteur de l'observation</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-result.intervalleReference</t>
+    <t>Limite inférieure de l'intervalle</t>
+  </si>
+  <si>
+    <t>(preferred): UCUM for units</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.referenceRange.high</t>
+  </si>
+  <si>
+    <t>Limite supérieure de l'intervalle</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.referenceRange.normalValue</t>
+  </si>
+  <si>
+    <t>Valeur normale si pertinente pour l'intervalle</t>
+  </si>
+  <si>
+    <t>(preferred): SNOMED CT</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.referenceRange.type</t>
+  </si>
+  <si>
+    <t>Type d'intervalle de référence</t>
+  </si>
+  <si>
+    <t>(preferred): HL7 Observation Reference Range Meaning Codes</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.referenceRange.appliesTo</t>
+  </si>
+  <si>
+    <t>Population concernée pour cet intervalle</t>
+  </si>
+  <si>
+    <t>(preferred): SNOMED CT, HL7 v3-Race</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.referenceRange.age</t>
   </si>
   <si>
     <t xml:space="preserve">Range
 </t>
   </si>
   <si>
-    <t>Intervalle de référence</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-result.commentaires</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-commentaire-er
-</t>
-  </si>
-  <si>
-    <t>entrée Commentaires</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-result.demandeExamen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-demande-examen-ou-suivi
-</t>
-  </si>
-  <si>
-    <t>Demande d'examen associée</t>
+    <t>Tranche d'âge pour cet intervalle</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.referenceRange.text</t>
+  </si>
+  <si>
+    <t>Texte libre</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.interpretation</t>
+  </si>
+  <si>
+    <t>Interprétation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.note</t>
+  </si>
+  <si>
+    <t>Commentaire</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.component</t>
+  </si>
+  <si>
+    <t>Composant dans le cas d'une observation composée de plusieurs sous-observations</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.derivedFrom[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-laboratory-observationhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-imaging-study</t>
+  </si>
+  <si>
+    <t>Référence de la resource à partir de laquelle l'observation a été faite. Par exemple, une image échographique à partir de laquelle une mesure fœtale est réalisée.</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-result.hasMember[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-laboratory-observation
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation</t>
+  </si>
+  <si>
+    <t>Cette observation est un groupe d'observations (par exemple, une batterie de tests, un ensemble de mesures de signes vitaux).</t>
   </si>
 </sst>
 </file>
@@ -664,11 +936,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.45703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.45703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.87109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="55.87109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -677,7 +949,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.82421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -691,14 +963,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="50.2578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.45703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -999,7 +1271,7 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
@@ -1016,10 +1288,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1042,13 +1314,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1099,7 +1371,7 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
@@ -1116,10 +1388,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1127,10 +1399,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1142,13 +1414,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1199,13 +1471,13 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1216,10 +1488,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1227,10 +1499,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1242,13 +1514,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1299,13 +1571,13 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1316,10 +1588,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1327,10 +1599,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1342,13 +1614,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1399,13 +1671,13 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1416,10 +1688,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1427,10 +1699,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1442,13 +1714,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1499,13 +1771,13 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
@@ -1516,10 +1788,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1530,7 +1802,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1542,13 +1814,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1599,13 +1871,13 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1616,10 +1888,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1630,7 +1902,7 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>73</v>
@@ -1642,13 +1914,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1699,13 +1971,13 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>73</v>
@@ -1716,10 +1988,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1742,13 +2014,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1799,7 +2071,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1816,10 +2088,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1842,13 +2114,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1899,7 +2171,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1916,10 +2188,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1942,13 +2214,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1999,7 +2271,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2016,10 +2288,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2042,13 +2314,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2099,7 +2371,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2111,6 +2383,2706 @@
         <v>73</v>
       </c>
       <c r="AJ14" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-result.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-result.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="201">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -520,6 +520,10 @@
   </si>
   <si>
     <t>fr-lm-observation-result.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>Localisation anatomique</t>
@@ -3614,13 +3618,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3688,10 +3692,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3717,10 +3721,10 @@
         <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3771,7 +3775,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -3788,10 +3792,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3817,10 +3821,10 @@
         <v>80</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3871,7 +3875,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3888,10 +3892,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3914,13 +3918,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3950,7 +3954,7 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>73</v>
@@ -3971,7 +3975,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3988,10 +3992,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4014,13 +4018,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4050,7 +4054,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4071,7 +4075,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4088,10 +4092,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4117,10 +4121,10 @@
         <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4150,7 +4154,7 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>73</v>
@@ -4171,7 +4175,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4188,10 +4192,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4217,10 +4221,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4250,7 +4254,7 @@
         <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z33" t="s" s="2">
         <v>73</v>
@@ -4271,7 +4275,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4288,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4317,10 +4321,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4350,7 +4354,7 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4371,7 +4375,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4388,10 +4392,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4414,13 +4418,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4450,7 +4454,7 @@
         <v>73</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -4471,7 +4475,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4488,10 +4492,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4517,10 +4521,10 @@
         <v>152</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4571,7 +4575,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4588,10 +4592,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4617,10 +4621,10 @@
         <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4671,7 +4675,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -4688,10 +4692,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4717,10 +4721,10 @@
         <v>152</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4771,7 +4775,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4788,10 +4792,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4817,10 +4821,10 @@
         <v>80</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4871,7 +4875,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4888,10 +4892,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4914,13 +4918,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4971,7 +4975,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -4988,10 +4992,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5014,13 +5018,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5071,7 +5075,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-result.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-result.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-observation-result.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-observation-result.header.langue</t>
+    <t>fr-lm-observation-result.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,13 +451,13 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-observation-result.directSubject[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-devicehttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professionalhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedure</t>
   </si>
   <si>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-result.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-result.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="200">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,10 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut de l'observation</t>
+  </si>
+  <si>
+    <t>Statut</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -968,7 +965,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="50.2578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2624,7 +2621,7 @@
         <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2654,31 +2651,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2692,10 +2689,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2721,10 +2718,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2775,7 +2772,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2792,10 +2789,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2821,10 +2818,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2875,7 +2872,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2892,10 +2889,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2918,13 +2915,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>144</v>
-      </c>
       <c r="M20" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2975,7 +2972,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2992,10 +2989,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3018,13 +3015,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>147</v>
-      </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3075,7 +3072,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3092,10 +3089,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3121,10 +3118,10 @@
         <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3154,7 +3151,7 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
@@ -3175,7 +3172,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3192,10 +3189,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3218,13 +3215,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>153</v>
-      </c>
       <c r="M23" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3275,7 +3272,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3292,10 +3289,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3321,10 +3318,10 @@
         <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3375,7 +3372,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3392,10 +3389,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3418,13 +3415,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>158</v>
-      </c>
       <c r="M25" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3475,7 +3472,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3492,10 +3489,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3518,13 +3515,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="M26" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3575,7 +3572,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3592,10 +3589,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3618,13 +3615,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="M27" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3675,7 +3672,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3692,10 +3689,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3721,10 +3718,10 @@
         <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3775,7 +3772,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -3792,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3821,10 +3818,10 @@
         <v>80</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3875,7 +3872,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3892,10 +3889,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3918,13 +3915,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="M30" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3954,7 +3951,7 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>73</v>
@@ -3975,7 +3972,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3992,10 +3989,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4018,13 +4015,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4054,28 +4051,28 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4092,10 +4089,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4121,10 +4118,10 @@
         <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4154,7 +4151,7 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>73</v>
@@ -4175,7 +4172,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4192,10 +4189,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4221,10 +4218,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4254,7 +4251,7 @@
         <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Z33" t="s" s="2">
         <v>73</v>
@@ -4275,7 +4272,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4292,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4321,10 +4318,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4354,7 +4351,7 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4375,7 +4372,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4392,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4418,13 +4415,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="M35" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4454,7 +4451,7 @@
         <v>73</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -4475,7 +4472,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4492,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4518,13 +4515,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4575,7 +4572,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4592,10 +4589,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4621,10 +4618,10 @@
         <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4675,7 +4672,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -4692,10 +4689,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4718,13 +4715,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4775,7 +4772,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4792,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4821,10 +4818,10 @@
         <v>80</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4875,7 +4872,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4892,10 +4889,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4918,13 +4915,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L40" t="s" s="2">
-        <v>197</v>
-      </c>
       <c r="M40" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4975,7 +4972,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -4992,10 +4989,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5018,13 +5015,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L41" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="M41" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5075,7 +5072,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-result.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-result.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
